--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_05-09-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_05-09-2025.xlsx
@@ -1358,7 +1358,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 522 Server Error: &lt;none&gt; for url: https://imperialhouse-nj.com/contact-us-2/</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 525 Server Error: &lt;none&gt; for url: https://www.directinsulation.com/product-page/celotex-ga4080-2400x1200x80mm</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 525 Server Error: &lt;none&gt; for url: https://www.directinsulation.com/product-page/celotex-ga4090-2400x1200x90mm</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 525 Server Error: &lt;none&gt; for url: https://www.directinsulation.com/product-page/celotex-ga4100-2400x1200x100mm</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 525 Server Error: &lt;none&gt; for url: https://www.directinsulation.com/product-page/celotex-xr4110-insulation-2400x1200x110mm</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 525 Server Error: &lt;none&gt; for url: https://tiffanynacke.org/</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 525 Server Error: &lt;none&gt; for url: https://www.directinsulation.com/product-page/celotex-xr4130-2400x1200x130mm</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 525 Server Error: &lt;none&gt; for url: https://www.directinsulation.com/product-page/celotex-xr4140-2400x1200x140mm</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 525 Server Error: &lt;none&gt; for url: https://www.directinsulation.com/product-page/celotex-xr4150-2400x1200x150mm</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 525 Server Error: &lt;none&gt; for url: https://www.directinsulation.com/product-page/celotex-pl4025-ins-plasterboard-25mm-12-5mm</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 525 Server Error: &lt;none&gt; for url: https://www.directinsulation.com/product-page/celotex-pl4050-ins-plasterboard-50mm-12-5mm</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>£58.00</t>
+          <t>£55.00</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>£61.00</t>
+          <t>£55.00</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 525 Server Error: &lt;none&gt; for url: https://www.directinsulation.com/product-page/celotex-cavity-cw4075-450mm-x-1200mm-pack-of-8</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>£58.00</t>
+          <t>£52.00</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 525 Server Error: &lt;none&gt; for url: https://tiffanynacke.org/</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>£1280.0</t>
+          <t>£1248.0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>£1360.0</t>
+          <t>£1328.0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
